--- a/config/3.3大集中指标比较拆分_配置.xlsx
+++ b/config/3.3大集中指标比较拆分_配置.xlsx
@@ -185,6 +185,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>审核工具</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>是否启用写入：留空或填“是”=该报表正常拆分写入；填“否”=该报表不写入（即使比较结果有数据）。取值写错时「检查配置」会提示。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -788,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,9 +827,15 @@
           <t>批次</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>是否启用写入</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
